--- a/mission_log_test.xlsx
+++ b/mission_log_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,27 +1410,1773 @@
           <t>1 - TRIVIAL</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>20-05-2025 10:04:35</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-09-2025 16:07:10</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>02-09-2025 16:07:26</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-09-2025 16:07:31</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>150</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-09-2025 16:08:21</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:19:42</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>150</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:20:03</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>150</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:22:35</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:40:05</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>150</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:41:21</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>150</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:44:44</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>150</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:45:04</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>150</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:45:27</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>150</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:46:05</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SES Herald of Wrath</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CalamitusXIII</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>150</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SUPER PRIVATE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mirin Sector</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hellmire</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Spore Burst Strain</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>High-Priority</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Blitz: Secure Research Site</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>10 - SUPER HELLDIVE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-09-2025 19:46:39</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SES Adjudicator of Allegiance</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CADET</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Akira Sector</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Alaraph</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Automaton Legion</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Terminate Illegal Broadcast</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1 - TRIVIAL</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>02-09-2025 21:02:12</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SES Adjudicator of Allegiance</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CADET</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Akira Sector</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Alaraph</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Automaton Legion</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Terminate Illegal Broadcast</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1 - TRIVIAL</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>02-09-2025 21:03:57</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SES Adjudicator of Allegiance</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CADET</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Akira Sector</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Alaraph</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Automaton Legion</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Terminate Illegal Broadcast</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1 - TRIVIAL</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>Outstanding Patriotism</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>20-05-2025 10:04:35</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>02-09-2025 21:04:07</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SES Adjudicator of Allegiance</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CADET</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Akira Sector</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Alaraph</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Automatons</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Automaton Legion</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Terminate Illegal Broadcast</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1 - TRIVIAL</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-09-2025 21:04:08</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SES Adjudicator of Allegiance</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CADET</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Akira Sector</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Alaraph</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Planet Surface</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Terminids</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rupture Strain &amp; Hive Lords</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Terminate Illegal Broadcast</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1 - TRIVIAL</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Outstanding Patriotism</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>02-09-2025 22:36:19</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
